--- a/time.xlsx
+++ b/time.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maiken\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187CC394-0736-42E8-9725-26A2E8D55885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E28828-1C90-45C5-B0D5-894520BA37D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="32505" xr2:uid="{6EE1C5DF-FBAC-49D0-AAB6-C137180BF98C}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="23985" xr2:uid="{6EE1C5DF-FBAC-49D0-AAB6-C137180BF98C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -134,10 +134,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>コミュスト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>W</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -268,10 +264,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>デザテク</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>鳥飼</t>
     <rPh sb="0" eb="2">
       <t>トリカイ</t>
@@ -326,13 +318,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>情リテ</t>
-    <rPh sb="0" eb="1">
-      <t>ジョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>岩城</t>
     <rPh sb="0" eb="2">
       <t>イワシロ</t>
@@ -341,13 +326,6 @@
   </si>
   <si>
     <t>H3844</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>体育Ⅳ</t>
-    <rPh sb="0" eb="2">
-      <t>タイイク</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -434,6 +412,40 @@
     <rPh sb="6" eb="8">
       <t>エンシュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デザインとテクノロジー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報リテラシーと表現技術</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ギジュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スポーツ健康科学実習Ⅳ</t>
+    <rPh sb="4" eb="6">
+      <t>ケンコウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カガク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コミュニケーションストラテジー</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -931,7 +943,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -954,10 +966,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -980,7 +992,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -992,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>201</v>
@@ -1003,16 +1015,16 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1029,16 +1041,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1055,16 +1067,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -1081,16 +1093,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1107,16 +1119,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
         <v>34</v>
       </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1133,22 +1145,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
         <v>37</v>
       </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>204</v>
@@ -1159,22 +1171,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
         <v>40</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>41</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>304</v>
@@ -1185,16 +1197,16 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1211,25 +1223,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -1237,16 +1249,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E14">
         <v>4</v>
@@ -1263,16 +1275,16 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -1289,16 +1301,16 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E16">
         <v>3</v>

--- a/time.xlsx
+++ b/time.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maiken\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E28828-1C90-45C5-B0D5-894520BA37D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4B625B-F709-477A-A7F7-449A2CAA4265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="23985" xr2:uid="{6EE1C5DF-FBAC-49D0-AAB6-C137180BF98C}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="32505" xr2:uid="{6EE1C5DF-FBAC-49D0-AAB6-C137180BF98C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="76">
   <si>
     <t>授業コード</t>
     <rPh sb="0" eb="2">
@@ -446,6 +446,100 @@
   </si>
   <si>
     <t>コミュニケーションストラテジー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H3045</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H3046</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H3530</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドレンビル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>花﨑</t>
+    <rPh sb="0" eb="2">
+      <t>ハナサキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>渡邊</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H3090</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">H3102 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パーソナリティ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>伊藤ひ</t>
+    <rPh sb="0" eb="2">
+      <t>イトウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H3573</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文章作法</t>
+    <rPh sb="0" eb="2">
+      <t>ブンショウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>矢口</t>
+    <rPh sb="0" eb="2">
+      <t>ヤグチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>H3087</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>哲学入門</t>
+    <rPh sb="0" eb="2">
+      <t>テツガク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニュウモン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>美頭</t>
+    <rPh sb="0" eb="1">
+      <t>ウツク</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>アタマ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -898,7 +992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0E84CA3-9BA8-46B5-94E6-A659A4AFFE12}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" customWidth="1"/>
@@ -1325,6 +1419,188 @@
         <v>2</v>
       </c>
     </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>112</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18">
+        <v>110</v>
+      </c>
+      <c r="H18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>111</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>202</v>
+      </c>
+      <c r="H20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>201</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>303</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>202</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
